--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260910.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260910.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>4.09%</t>
+          <t>4.16%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.84%</t>
+          <t>3.87%</t>
         </is>
       </c>
     </row>
@@ -660,46 +660,46 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>6,282,000</t>
+          <t>37,056,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>37,056,000</t>
+          <t>49,710,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -711,17 +711,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>49,710,000</t>
+          <t>6,282,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -733,39 +733,39 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>10,202,000</t>
+          <t>4,367,438,146</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.92%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>4,168,628,656</t>
+          <t>10,202,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
@@ -858,134 +858,134 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>202609WTX</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>115/09台股期貨</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>35,990,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>202609WTX</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>115/09台股期貨</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>35,990,000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>4,004,000</t>
+          <t>6,846,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.41%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>6,846,000</t>
+          <t>33,103,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>23,080,000</t>
+          <t>4,004,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>33,103,000</t>
+          <t>42,300,500</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,44 +997,44 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>42,300,500</t>
+          <t>9,766,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>9,766,000</t>
+          <t>23,080,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,270,000</t>
+          <t>9,594,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,44 +1085,44 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>9,594,000</t>
+          <t>2,939,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,939,000</t>
+          <t>2,270,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
@@ -1144,51 +1144,51 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>14,684,000</t>
+          <t>18,088,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>18,088,000</t>
+          <t>14,684,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,741,179,590</t>
+          <t>2,706,859,590</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -1415,44 +1415,44 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>10,287,000</t>
+          <t>9,344,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>9,344,000</t>
+          <t>10,287,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -1584,90 +1584,90 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>202610WTX</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>115/10台股期貨</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>48,390,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>202610WTX</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>115/10台股期貨</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>48,390,000</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1,593,000</t>
+          <t>52,799,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>52,799,000</t>
+          <t>1,593,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16,919,045</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
     </row>
